--- a/form nhập đề.xlsx
+++ b/form nhập đề.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HTML\Drop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC892F5-A161-427E-A602-B3372416D206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FDF5BA-6DA0-4B6B-A507-C4AA1498C1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -368,11 +368,64 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -383,10 +436,30 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -395,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -403,47 +476,74 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -668,7 +768,7 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="63" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" customWidth="1"/>
     <col min="4" max="4" width="25.109375" customWidth="1"/>
     <col min="5" max="5" width="25.21875" customWidth="1"/>
     <col min="6" max="6" width="25.33203125" customWidth="1"/>
@@ -676,70 +776,70 @@
     <col min="8" max="8" width="37.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="17" customFormat="1" ht="42">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="42.6" thickBot="1">
+      <c r="A1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="13" t="s">
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
     </row>
     <row r="2" spans="1:28" ht="15.6">
-      <c r="A2" s="5">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="3"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -760,28 +860,28 @@
       <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
     </row>
-    <row r="3" spans="1:28" ht="15.6">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6" t="s">
+    <row r="3" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A3" s="13"/>
+      <c r="B3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="4"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="6"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -803,29 +903,29 @@
       <c r="AB3" s="2"/>
     </row>
     <row r="4" spans="1:28" ht="15.6">
-      <c r="A4" s="5">
+      <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -846,28 +946,28 @@
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
     </row>
-    <row r="5" spans="1:28" ht="15.6">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6" t="s">
+    <row r="5" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A5" s="13"/>
+      <c r="B5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="4"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="6"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -889,29 +989,29 @@
       <c r="AB5" s="2"/>
     </row>
     <row r="6" spans="1:28" ht="15.6">
-      <c r="A6" s="5">
+      <c r="A6" s="12">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -932,28 +1032,28 @@
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
     </row>
-    <row r="7" spans="1:28" ht="15.6">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6" t="s">
+    <row r="7" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A7" s="13"/>
+      <c r="B7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="4"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="6"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -975,29 +1075,29 @@
       <c r="AB7" s="2"/>
     </row>
     <row r="8" spans="1:28" ht="15.6">
-      <c r="A8" s="5">
+      <c r="A8" s="12">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -1018,28 +1118,28 @@
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
     </row>
-    <row r="9" spans="1:28" ht="15.6">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
+    <row r="9" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A9" s="13"/>
+      <c r="B9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="4"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="6"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -1061,27 +1161,27 @@
       <c r="AB9" s="2"/>
     </row>
     <row r="10" spans="1:28" ht="15.6">
-      <c r="A10" s="5">
+      <c r="A10" s="12">
         <v>5</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="3"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1102,26 +1202,26 @@
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
     </row>
-    <row r="11" spans="1:28" ht="15.6">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6" t="s">
+    <row r="11" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A11" s="13"/>
+      <c r="B11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="4"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="6"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -1143,27 +1243,27 @@
       <c r="AB11" s="2"/>
     </row>
     <row r="12" spans="1:28" ht="15.6">
-      <c r="A12" s="5">
+      <c r="A12" s="12">
         <v>6</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="3"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -1184,26 +1284,26 @@
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
     </row>
-    <row r="13" spans="1:28" ht="15.6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A13" s="13"/>
+      <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="19"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="4"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="6"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -1225,27 +1325,27 @@
       <c r="AB13" s="2"/>
     </row>
     <row r="14" spans="1:28" ht="15.6">
-      <c r="A14" s="5">
+      <c r="A14" s="12">
         <v>7</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="3"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -1266,26 +1366,26 @@
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
     </row>
-    <row r="15" spans="1:28" ht="15.6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6" t="s">
+    <row r="15" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A15" s="13"/>
+      <c r="B15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="4"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="6"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -1307,25 +1407,25 @@
       <c r="AB15" s="2"/>
     </row>
     <row r="16" spans="1:28" ht="15.6">
-      <c r="A16" s="5">
+      <c r="A16" s="12">
         <v>8</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="3"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="5"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -1346,24 +1446,24 @@
       <c r="AA16" s="2"/>
       <c r="AB16" s="2"/>
     </row>
-    <row r="17" spans="1:28" ht="15.6">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6" t="s">
+    <row r="17" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A17" s="13"/>
+      <c r="B17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="4"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="6"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -29864,14 +29964,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="I14:I15"/>
     <mergeCell ref="I16:I17"/>
     <mergeCell ref="D1:G1"/>
@@ -29881,6 +29973,14 @@
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/form nhập đề.xlsx
+++ b/form nhập đề.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HTML\Drop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FDF5BA-6DA0-4B6B-A507-C4AA1498C1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F372F6CA-8C7C-41A9-BC26-55ACA6F8430A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>CÂU HỎI</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>HÌNH ẢNH/VIDEO/ÂM THANH</t>
-  </si>
-  <si>
-    <t>STT</t>
   </si>
   <si>
     <t xml:space="preserve">Chủ đề </t>
@@ -88,13 +85,7 @@
     <t>q1</t>
   </si>
   <si>
-    <t>q2</t>
-  </si>
-  <si>
     <t>q3</t>
-  </si>
-  <si>
-    <t>q4</t>
   </si>
   <si>
     <t>a1</t>
@@ -257,6 +248,60 @@
   </si>
   <si>
     <t>d8</t>
+  </si>
+  <si>
+    <t>vòng</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>ques1</t>
+  </si>
+  <si>
+    <t>ques2</t>
+  </si>
+  <si>
+    <t>ques3</t>
+  </si>
+  <si>
+    <t>ques4</t>
+  </si>
+  <si>
+    <t>ques5</t>
+  </si>
+  <si>
+    <t>ques6</t>
+  </si>
+  <si>
+    <t>ques7</t>
+  </si>
+  <si>
+    <t>ques8</t>
+  </si>
+  <si>
+    <t>ques9</t>
+  </si>
+  <si>
+    <t>ques10</t>
+  </si>
+  <si>
+    <t>ques11</t>
+  </si>
+  <si>
+    <t>ques12</t>
+  </si>
+  <si>
+    <t>ques13</t>
+  </si>
+  <si>
+    <t>ques14</t>
+  </si>
+  <si>
+    <t>ques15</t>
+  </si>
+  <si>
+    <t>ques16</t>
   </si>
 </sst>
 </file>
@@ -480,10 +525,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -498,12 +539,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -535,17 +570,27 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -777,22 +822,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="4" customFormat="1" ht="42.6" thickBot="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="28" t="s">
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="22" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="3"/>
@@ -816,30 +861,30 @@
       <c r="AA1" s="3"/>
       <c r="AB1" s="3"/>
     </row>
-    <row r="2" spans="1:28" ht="15.6">
-      <c r="A2" s="12">
+    <row r="2" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A2" s="23">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>5</v>
+      <c r="B2" s="8" t="s">
+        <v>4</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>21</v>
+      <c r="C2" s="16" t="s">
+        <v>78</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>25</v>
+      <c r="D2" s="16" t="s">
+        <v>22</v>
       </c>
-      <c r="E2" s="22" t="s">
-        <v>41</v>
+      <c r="E2" s="18" t="s">
+        <v>38</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>57</v>
+      <c r="F2" s="16" t="s">
+        <v>54</v>
       </c>
-      <c r="G2" s="20" t="s">
-        <v>71</v>
+      <c r="G2" s="16" t="s">
+        <v>68</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="5"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="25"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -861,27 +906,27 @@
       <c r="AB2" s="2"/>
     </row>
     <row r="3" spans="1:28" ht="16.2" thickBot="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="11" t="s">
-        <v>6</v>
+      <c r="A3" s="24"/>
+      <c r="B3" s="9" t="s">
+        <v>5</v>
       </c>
-      <c r="C3" s="21" t="s">
-        <v>22</v>
+      <c r="C3" s="16" t="s">
+        <v>79</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>26</v>
+      <c r="D3" s="17" t="s">
+        <v>23</v>
       </c>
-      <c r="E3" s="23" t="s">
-        <v>42</v>
+      <c r="E3" s="19" t="s">
+        <v>39</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>58</v>
+      <c r="F3" s="17" t="s">
+        <v>55</v>
       </c>
-      <c r="G3" s="21" t="s">
-        <v>72</v>
+      <c r="G3" s="17" t="s">
+        <v>69</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="6"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="26"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -902,30 +947,30 @@
       <c r="AA3" s="2"/>
       <c r="AB3" s="2"/>
     </row>
-    <row r="4" spans="1:28" ht="15.6">
-      <c r="A4" s="12">
+    <row r="4" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A4" s="23">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>7</v>
+      <c r="B4" s="8" t="s">
+        <v>6</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>23</v>
+      <c r="C4" s="16" t="s">
+        <v>80</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>27</v>
+      <c r="D4" s="16" t="s">
+        <v>24</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>43</v>
+      <c r="E4" s="18" t="s">
+        <v>40</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>59</v>
+      <c r="F4" s="16" t="s">
+        <v>56</v>
       </c>
-      <c r="G4" s="20" t="s">
-        <v>73</v>
+      <c r="G4" s="16" t="s">
+        <v>70</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="5"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="25"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -947,27 +992,27 @@
       <c r="AB4" s="2"/>
     </row>
     <row r="5" spans="1:28" ht="16.2" thickBot="1">
-      <c r="A5" s="13"/>
-      <c r="B5" s="11" t="s">
-        <v>8</v>
+      <c r="A5" s="24"/>
+      <c r="B5" s="9" t="s">
+        <v>7</v>
       </c>
-      <c r="C5" s="21" t="s">
-        <v>24</v>
+      <c r="C5" s="16" t="s">
+        <v>81</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>28</v>
+      <c r="D5" s="17" t="s">
+        <v>25</v>
       </c>
-      <c r="E5" s="23" t="s">
-        <v>44</v>
+      <c r="E5" s="19" t="s">
+        <v>41</v>
       </c>
-      <c r="F5" s="21" t="s">
-        <v>60</v>
+      <c r="F5" s="17" t="s">
+        <v>57</v>
       </c>
-      <c r="G5" s="21" t="s">
-        <v>74</v>
+      <c r="G5" s="17" t="s">
+        <v>71</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="6"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="26"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -988,30 +1033,30 @@
       <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
     </row>
-    <row r="6" spans="1:28" ht="15.6">
-      <c r="A6" s="12">
+    <row r="6" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A6" s="23">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>9</v>
+      <c r="B6" s="8" t="s">
+        <v>8</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>21</v>
+      <c r="C6" s="16" t="s">
+        <v>82</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>29</v>
+      <c r="D6" s="16" t="s">
+        <v>26</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>45</v>
+      <c r="E6" s="18" t="s">
+        <v>42</v>
       </c>
-      <c r="F6" s="20" t="s">
-        <v>61</v>
+      <c r="F6" s="16" t="s">
+        <v>58</v>
       </c>
-      <c r="G6" s="20" t="s">
-        <v>75</v>
+      <c r="G6" s="16" t="s">
+        <v>72</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="5"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="25"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1033,27 +1078,27 @@
       <c r="AB6" s="2"/>
     </row>
     <row r="7" spans="1:28" ht="16.2" thickBot="1">
-      <c r="A7" s="13"/>
-      <c r="B7" s="11" t="s">
-        <v>10</v>
+      <c r="A7" s="24"/>
+      <c r="B7" s="9" t="s">
+        <v>9</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>22</v>
+      <c r="C7" s="16" t="s">
+        <v>83</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>30</v>
+      <c r="D7" s="17" t="s">
+        <v>27</v>
       </c>
-      <c r="E7" s="23" t="s">
-        <v>46</v>
+      <c r="E7" s="19" t="s">
+        <v>43</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>62</v>
+      <c r="F7" s="17" t="s">
+        <v>59</v>
       </c>
-      <c r="G7" s="21" t="s">
-        <v>76</v>
+      <c r="G7" s="17" t="s">
+        <v>73</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="6"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="26"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -1074,30 +1119,30 @@
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
     </row>
-    <row r="8" spans="1:28" ht="15.6">
-      <c r="A8" s="12">
+    <row r="8" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A8" s="23">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>11</v>
+      <c r="B8" s="8" t="s">
+        <v>10</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>23</v>
+      <c r="C8" s="16" t="s">
+        <v>84</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>31</v>
+      <c r="D8" s="16" t="s">
+        <v>28</v>
       </c>
-      <c r="E8" s="22" t="s">
-        <v>47</v>
+      <c r="E8" s="18" t="s">
+        <v>44</v>
       </c>
-      <c r="F8" s="20" t="s">
-        <v>63</v>
+      <c r="F8" s="16" t="s">
+        <v>60</v>
       </c>
-      <c r="G8" s="20" t="s">
-        <v>77</v>
+      <c r="G8" s="16" t="s">
+        <v>74</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="5"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="25"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -1119,27 +1164,27 @@
       <c r="AB8" s="2"/>
     </row>
     <row r="9" spans="1:28" ht="16.2" thickBot="1">
-      <c r="A9" s="13"/>
-      <c r="B9" s="11" t="s">
-        <v>12</v>
+      <c r="A9" s="24"/>
+      <c r="B9" s="9" t="s">
+        <v>11</v>
       </c>
-      <c r="C9" s="21" t="s">
-        <v>24</v>
+      <c r="C9" s="16" t="s">
+        <v>85</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>32</v>
+      <c r="D9" s="17" t="s">
+        <v>29</v>
       </c>
-      <c r="E9" s="23" t="s">
-        <v>48</v>
+      <c r="E9" s="19" t="s">
+        <v>45</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>64</v>
+      <c r="F9" s="17" t="s">
+        <v>61</v>
       </c>
-      <c r="G9" s="21" t="s">
-        <v>78</v>
+      <c r="G9" s="17" t="s">
+        <v>75</v>
       </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="6"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="26"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -1160,28 +1205,28 @@
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
     </row>
-    <row r="10" spans="1:28" ht="15.6">
-      <c r="A10" s="12">
+    <row r="10" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A10" s="23">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>13</v>
+      <c r="B10" s="8" t="s">
+        <v>12</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>21</v>
+      <c r="C10" s="16" t="s">
+        <v>86</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>33</v>
+      <c r="D10" s="16" t="s">
+        <v>30</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>49</v>
+      <c r="E10" s="18" t="s">
+        <v>46</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>65</v>
+      <c r="F10" s="16" t="s">
+        <v>62</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1203,25 +1248,25 @@
       <c r="AB10" s="2"/>
     </row>
     <row r="11" spans="1:28" ht="16.2" thickBot="1">
-      <c r="A11" s="13"/>
-      <c r="B11" s="11" t="s">
-        <v>14</v>
+      <c r="A11" s="24"/>
+      <c r="B11" s="9" t="s">
+        <v>13</v>
       </c>
-      <c r="C11" s="21" t="s">
-        <v>22</v>
+      <c r="C11" s="16" t="s">
+        <v>87</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>34</v>
+      <c r="D11" s="17" t="s">
+        <v>31</v>
       </c>
-      <c r="E11" s="23" t="s">
-        <v>50</v>
+      <c r="E11" s="19" t="s">
+        <v>47</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>66</v>
+      <c r="F11" s="17" t="s">
+        <v>63</v>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="26"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -1242,28 +1287,28 @@
       <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
     </row>
-    <row r="12" spans="1:28" ht="15.6">
-      <c r="A12" s="12">
+    <row r="12" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A12" s="23">
         <v>6</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>15</v>
+      <c r="B12" s="8" t="s">
+        <v>14</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>23</v>
+      <c r="C12" s="16" t="s">
+        <v>88</v>
       </c>
-      <c r="D12" s="20" t="s">
-        <v>35</v>
+      <c r="D12" s="16" t="s">
+        <v>32</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>51</v>
+      <c r="E12" s="18" t="s">
+        <v>48</v>
       </c>
-      <c r="F12" s="20" t="s">
-        <v>67</v>
+      <c r="F12" s="16" t="s">
+        <v>64</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="25"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -1285,25 +1330,25 @@
       <c r="AB12" s="2"/>
     </row>
     <row r="13" spans="1:28" ht="16.2" thickBot="1">
-      <c r="A13" s="13"/>
-      <c r="B13" s="11" t="s">
-        <v>16</v>
+      <c r="A13" s="24"/>
+      <c r="B13" s="9" t="s">
+        <v>15</v>
       </c>
-      <c r="C13" s="21" t="s">
-        <v>24</v>
+      <c r="C13" s="16" t="s">
+        <v>89</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>36</v>
+      <c r="D13" s="17" t="s">
+        <v>33</v>
       </c>
-      <c r="E13" s="23" t="s">
-        <v>52</v>
+      <c r="E13" s="19" t="s">
+        <v>49</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>68</v>
+      <c r="F13" s="17" t="s">
+        <v>65</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="26"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -1324,28 +1369,28 @@
       <c r="AA13" s="2"/>
       <c r="AB13" s="2"/>
     </row>
-    <row r="14" spans="1:28" ht="15.6">
-      <c r="A14" s="12">
+    <row r="14" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A14" s="23">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>17</v>
+      <c r="B14" s="8" t="s">
+        <v>16</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>21</v>
+      <c r="C14" s="16" t="s">
+        <v>90</v>
       </c>
-      <c r="D14" s="20" t="s">
-        <v>37</v>
+      <c r="D14" s="16" t="s">
+        <v>34</v>
       </c>
-      <c r="E14" s="22" t="s">
-        <v>53</v>
+      <c r="E14" s="18" t="s">
+        <v>50</v>
       </c>
-      <c r="F14" s="20" t="s">
-        <v>69</v>
+      <c r="F14" s="16" t="s">
+        <v>66</v>
       </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="25"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -1367,25 +1412,25 @@
       <c r="AB14" s="2"/>
     </row>
     <row r="15" spans="1:28" ht="16.2" thickBot="1">
-      <c r="A15" s="13"/>
-      <c r="B15" s="11" t="s">
-        <v>18</v>
+      <c r="A15" s="24"/>
+      <c r="B15" s="9" t="s">
+        <v>17</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>22</v>
+      <c r="C15" s="16" t="s">
+        <v>91</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>38</v>
+      <c r="D15" s="17" t="s">
+        <v>35</v>
       </c>
-      <c r="E15" s="23" t="s">
-        <v>54</v>
+      <c r="E15" s="19" t="s">
+        <v>51</v>
       </c>
-      <c r="F15" s="21" t="s">
-        <v>70</v>
+      <c r="F15" s="17" t="s">
+        <v>67</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="6"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="26"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -1406,26 +1451,26 @@
       <c r="AA15" s="2"/>
       <c r="AB15" s="2"/>
     </row>
-    <row r="16" spans="1:28" ht="15.6">
-      <c r="A16" s="12">
+    <row r="16" spans="1:28" ht="16.2" thickBot="1">
+      <c r="A16" s="23">
         <v>8</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>19</v>
+      <c r="B16" s="8" t="s">
+        <v>18</v>
       </c>
-      <c r="C16" s="20" t="s">
-        <v>23</v>
+      <c r="C16" s="16" t="s">
+        <v>92</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>39</v>
+      <c r="D16" s="16" t="s">
+        <v>36</v>
       </c>
-      <c r="E16" s="22" t="s">
-        <v>55</v>
+      <c r="E16" s="18" t="s">
+        <v>52</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="25"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -1447,23 +1492,23 @@
       <c r="AB16" s="2"/>
     </row>
     <row r="17" spans="1:28" ht="16.2" thickBot="1">
-      <c r="A17" s="13"/>
-      <c r="B17" s="11" t="s">
-        <v>20</v>
+      <c r="A17" s="24"/>
+      <c r="B17" s="9" t="s">
+        <v>19</v>
       </c>
-      <c r="C17" s="21" t="s">
-        <v>24</v>
+      <c r="C17" s="16" t="s">
+        <v>93</v>
       </c>
-      <c r="D17" s="21" t="s">
-        <v>40</v>
+      <c r="D17" s="17" t="s">
+        <v>37</v>
       </c>
-      <c r="E17" s="23" t="s">
-        <v>56</v>
+      <c r="E17" s="19" t="s">
+        <v>53</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="26"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -1573,7 +1618,9 @@
     </row>
     <row r="21" spans="1:28" ht="15.6">
       <c r="B21" s="1"/>
-      <c r="C21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -1602,7 +1649,9 @@
     </row>
     <row r="22" spans="1:28" ht="15.6">
       <c r="B22" s="1"/>
-      <c r="C22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -1631,7 +1680,9 @@
     </row>
     <row r="23" spans="1:28" ht="15.6">
       <c r="B23" s="1"/>
-      <c r="C23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
